--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Observation EXAM, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA V EXAM (file 9000010.13) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="565">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -252,10 +252,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -597,6 +597,10 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-14:1589: fixed value "final" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -640,6 +644,10 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-15:1591: fixed value "http://terminology.hl7.org/CodeSystem/observation-category|exam" {null}</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
@@ -761,7 +769,7 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM (#9000010.13-.01 &gt; 9999999.15-)</t>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM – CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -876,10 +884,10 @@
     <t>FiveWs.context</t>
   </si>
   <si>
+    <t>1583: reference from V EXAM - VISIT (#9000010.13-.03)</t>
+  </si>
+  <si>
     <t>Outpat.VExam.VisitDateTime</t>
-  </si>
-  <si>
-    <t>1583: reference from V EXAM - VISIT (#9000010.13-.03)</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -931,10 +939,10 @@
 </t>
   </si>
   <si>
+    <t>1588: source value from V EXAM - EVENT DATE AND TIME (#9000010.13-1201)</t>
+  </si>
+  <si>
     <t>Outpat.VExam.EventDateTime</t>
-  </si>
-  <si>
-    <t>1588: source value from V EXAM - EVENT DATE AND TIME (#9000010.13-1201)</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1262,10 +1270,10 @@
     <t>363713009 |Has interpretation|</t>
   </si>
   <si>
+    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (#9000010.13-.04)</t>
+  </si>
+  <si>
     <t>Outpat.VExam.AbnormalNormal</t>
-  </si>
-  <si>
-    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (#9000010.13-.04)</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1355,10 +1363,10 @@
     <t>Act.text</t>
   </si>
   <si>
+    <t>1587: source value from V EXAM - COMMENTS (#9000010.13-81101)</t>
+  </si>
+  <si>
     <t>Outpat.VExam.Comments</t>
-  </si>
-  <si>
-    <t>1587: source value from V EXAM - COMMENTS (#9000010.13-81101)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2114,8 +2122,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="97.6640625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="99.87109375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3865,39 +3873,39 @@
         <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>192</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3920,19 +3928,19 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3960,10 +3968,10 @@
         <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
@@ -3981,7 +3989,7 @@
         <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3993,7 +4001,7 @@
         <v>84</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>84</v>
@@ -4005,31 +4013,31 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4048,19 +4056,19 @@
         <v>96</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
@@ -4085,13 +4093,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4109,7 +4117,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>95</v>
@@ -4124,22 +4132,22 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4150,10 +4158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4176,13 +4184,13 @@
         <v>84</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4233,7 +4241,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4257,7 +4265,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>84</v>
@@ -4274,10 +4282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4306,7 +4314,7 @@
         <v>142</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>144</v>
@@ -4347,19 +4355,19 @@
         <v>84</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4383,7 +4391,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>84</v>
@@ -4400,10 +4408,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4426,19 +4434,19 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -4487,7 +4495,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4508,10 +4516,10 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>84</v>
@@ -4520,18 +4528,18 @@
         <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>240</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4554,19 +4562,19 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4615,7 +4623,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4636,10 +4644,10 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>84</v>
@@ -4656,10 +4664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4682,19 +4690,19 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4743,7 +4751,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4758,36 +4766,36 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>259</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4810,16 +4818,16 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4869,7 +4877,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4890,13 +4898,13 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
@@ -4910,14 +4918,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4936,19 +4944,19 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4997,7 +5005,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5012,40 +5020,40 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5064,19 +5072,19 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5113,17 +5121,17 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5138,19 +5146,19 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5164,16 +5172,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5192,19 +5200,19 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5253,7 +5261,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5268,36 +5276,36 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5320,16 +5328,16 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5379,7 +5387,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5400,13 +5408,13 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5420,10 +5428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5446,17 +5454,17 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5505,7 +5513,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5520,36 +5528,36 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5572,19 +5580,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5621,17 +5629,17 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5640,7 +5648,7 @@
         <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>107</v>
@@ -5649,19 +5657,19 @@
         <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5672,13 +5680,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -5700,19 +5708,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5761,7 +5769,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5770,7 +5778,7 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
@@ -5779,33 +5787,33 @@
         <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5828,13 +5836,13 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5885,7 +5893,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5909,7 +5917,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -5926,10 +5934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5958,7 +5966,7 @@
         <v>142</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>144</v>
@@ -5999,19 +6007,19 @@
         <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6035,7 +6043,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6052,10 +6060,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6078,19 +6086,19 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6139,7 +6147,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6160,10 +6168,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6172,18 +6180,18 @@
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6209,20 +6217,20 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>84</v>
@@ -6246,10 +6254,10 @@
         <v>184</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6267,7 +6275,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6288,10 +6296,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6308,10 +6316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6334,17 +6342,17 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6393,7 +6401,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6414,10 +6422,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6434,10 +6442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6463,14 +6471,14 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6519,7 +6527,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6528,7 +6536,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6540,10 +6548,10 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
@@ -6560,10 +6568,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6589,16 +6597,16 @@
         <v>115</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6647,7 +6655,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6676,10 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6688,10 +6696,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6714,19 +6722,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6751,13 +6759,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6775,7 +6783,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6784,7 +6792,7 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
@@ -6799,7 +6807,7 @@
         <v>138</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
@@ -6816,14 +6824,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6842,19 +6850,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6879,13 +6887,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6903,7 +6911,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6921,33 +6929,33 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6970,19 +6978,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7031,7 +7039,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7052,10 +7060,10 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -7072,10 +7080,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7098,13 +7106,13 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7155,7 +7163,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7179,7 +7187,7 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7196,10 +7204,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7228,7 +7236,7 @@
         <v>142</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>144</v>
@@ -7269,19 +7277,19 @@
         <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7305,7 +7313,7 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
@@ -7322,10 +7330,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7348,16 +7356,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7407,7 +7415,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7431,7 +7439,7 @@
         <v>138</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7448,10 +7456,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7474,13 +7482,13 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7531,7 +7539,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7555,7 +7563,7 @@
         <v>138</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7572,10 +7580,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7598,13 +7606,13 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7655,7 +7663,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7679,7 +7687,7 @@
         <v>138</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7688,18 +7696,18 @@
         <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7722,16 +7730,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7757,13 +7765,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7781,7 +7789,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7799,19 +7807,19 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7822,10 +7830,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7848,19 +7856,19 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7885,13 +7893,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7909,7 +7917,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7930,10 +7938,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7950,10 +7958,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7976,16 +7984,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8035,7 +8043,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8053,19 +8061,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8076,10 +8084,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8102,16 +8110,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8161,7 +8169,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8179,19 +8187,19 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8202,10 +8210,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8228,19 +8236,19 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8289,7 +8297,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8301,7 +8309,7 @@
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8310,10 +8318,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8330,10 +8338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8356,13 +8364,13 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8413,7 +8421,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8437,7 +8445,7 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8454,10 +8462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8486,7 +8494,7 @@
         <v>142</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>144</v>
@@ -8539,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8563,7 +8571,7 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8580,14 +8588,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8609,10 +8617,10 @@
         <v>141</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>144</v>
@@ -8667,7 +8675,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8708,10 +8716,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8734,13 +8742,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8791,7 +8799,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8800,7 +8808,7 @@
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -8812,10 +8820,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8832,10 +8840,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8858,13 +8866,13 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8915,7 +8923,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8924,7 +8932,7 @@
         <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>107</v>
@@ -8936,10 +8944,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8956,10 +8964,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8982,19 +8990,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9022,10 +9030,10 @@
         <v>119</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9043,7 +9051,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9061,13 +9069,13 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9084,10 +9092,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9110,19 +9118,19 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9147,13 +9155,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9171,7 +9179,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9189,13 +9197,13 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9212,10 +9220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,17 +9246,17 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9297,7 +9305,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9321,7 +9329,7 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9338,10 +9346,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9364,13 +9372,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9421,7 +9429,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9442,10 +9450,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9462,10 +9470,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9488,16 +9496,16 @@
         <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9547,7 +9555,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9568,10 +9576,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9588,10 +9596,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9614,16 +9622,16 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9673,7 +9681,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9694,10 +9702,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9714,10 +9722,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9740,19 +9748,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9801,7 +9809,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9822,10 +9830,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9842,10 +9850,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9868,13 +9876,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9925,7 +9933,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9949,7 +9957,7 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -9966,10 +9974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9998,7 +10006,7 @@
         <v>142</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>144</v>
@@ -10051,7 +10059,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10075,7 +10083,7 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10092,14 +10100,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10121,10 +10129,10 @@
         <v>141</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>144</v>
@@ -10179,7 +10187,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10220,10 +10228,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10246,19 +10254,19 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10283,13 +10291,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10307,7 +10315,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>95</v>
@@ -10325,16 +10333,16 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>84</v>
@@ -10348,10 +10356,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10374,19 +10382,19 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10435,7 +10443,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10453,19 +10461,19 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10476,10 +10484,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10502,19 +10510,19 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10539,13 +10547,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10563,7 +10571,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10572,7 +10580,7 @@
         <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
@@ -10587,7 +10595,7 @@
         <v>138</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10604,14 +10612,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10630,19 +10638,19 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10667,13 +10675,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10691,7 +10699,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10709,19 +10717,19 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10732,10 +10740,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10761,16 +10769,16 @@
         <v>85</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10819,7 +10827,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10840,10 +10848,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -598,7 +598,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-14:1589: fixed value "final" {null}</t>
+inv-20:1589: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -645,7 +645,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-15:1591: fixed value "http://terminology.hl7.org/CodeSystem/observation-category|exam" {null}</t>
+inv-21:1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category|exam {null}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -598,7 +598,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-20:1589: fixed value = final {null}</t>
+inv-21:1589: fixed value = final {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -645,7 +645,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-21:1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category|exam {null}</t>
+inv-22:1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category|exam {null}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -769,7 +769,7 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM – CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210)</t>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -2122,7 +2122,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="99.87109375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="99.61328125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1668,7 +1668,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/docs/StructureDefinition-ObservationEXAMObservation.xlsx
+++ b/docs/StructureDefinition-ObservationEXAMObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA V EXAM (file 9000010.13) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V EXAM (#9000010.13) to Observation</t>
   </si>
   <si>
     <t>Purpose</t>
